--- a/doctool/test/auto/scenario23/システム機能設計書_サンプル_S23_expected.xlsx
+++ b/doctool/test/auto/scenario23/システム機能設計書_サンプル_S23_expected.xlsx
@@ -5,40 +5,39 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario23\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario22\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B97882-D93F-4126-9A46-6636EFB12B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74851ADB-FEE4-4550-B7BD-5ED0E19B2FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="エラーシート" sheetId="10" r:id="rId1"/>
-    <sheet name="レビュー結果1回目" sheetId="9" r:id="rId2"/>
-    <sheet name="表紙" sheetId="1" r:id="rId3"/>
-    <sheet name="変更履歴" sheetId="2" r:id="rId4"/>
-    <sheet name="目次" sheetId="3" r:id="rId5"/>
-    <sheet name="1.  画面取引定義" sheetId="4" r:id="rId6"/>
-    <sheet name="2. WA1020101(プロジェクト登録画面)" sheetId="5" r:id="rId7"/>
-    <sheet name="3. WA1020102(プロジェクト登録確認画面)" sheetId="6" r:id="rId8"/>
-    <sheet name="4. WA1020103(プロジェクト登録完了画面)" sheetId="7" r:id="rId9"/>
-    <sheet name="データ" sheetId="8" state="hidden" r:id="rId10"/>
+    <sheet name="レビュー結果1回目" sheetId="9" r:id="rId1"/>
+    <sheet name="表紙" sheetId="1" r:id="rId2"/>
+    <sheet name="変更履歴" sheetId="2" r:id="rId3"/>
+    <sheet name="目次" sheetId="3" r:id="rId4"/>
+    <sheet name="1.  画面取引定義" sheetId="4" r:id="rId5"/>
+    <sheet name="2. WA1020101(プロジェクト登録画面)" sheetId="5" r:id="rId6"/>
+    <sheet name="3. WA1020102(プロジェクト登録確認画面)" sheetId="6" r:id="rId7"/>
+    <sheet name="4. WA1020103(プロジェクト登録完了画面)" sheetId="7" r:id="rId8"/>
+    <sheet name="データ" sheetId="8" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_Toc46209822" localSheetId="5">'1.  画面取引定義'!$B$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'1.  画面取引定義'!$A$1:$AI$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'2. WA1020101(プロジェクト登録画面)'!$A$1:$AI$180</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'3. WA1020102(プロジェクト登録確認画面)'!$A$1:$AI$136</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'4. WA1020103(プロジェクト登録完了画面)'!$A$1:$AI$68</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">データ!$A$1:$E$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">レビュー結果1回目!$A$1:$K$18</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">表紙!$A$1:$S$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">目次!$A$1:$AI$33</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'1.  画面取引定義'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'2. WA1020101(プロジェクト登録画面)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'3. WA1020102(プロジェクト登録確認画面)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'4. WA1020103(プロジェクト登録完了画面)'!$1:$4</definedName>
+    <definedName name="_Toc46209822" localSheetId="4">'1.  画面取引定義'!$B$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'1.  画面取引定義'!$A$1:$AI$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'2. WA1020101(プロジェクト登録画面)'!$A$1:$AI$180</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'3. WA1020102(プロジェクト登録確認画面)'!$A$1:$AI$136</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'4. WA1020103(プロジェクト登録完了画面)'!$A$1:$AI$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">データ!$A$1:$E$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">レビュー結果1回目!$A$1:$K$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">表紙!$A$1:$S$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">変更履歴!$A$1:$AI$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">目次!$A$1:$AI$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'1.  画面取引定義'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'2. WA1020101(プロジェクト登録画面)'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'3. WA1020102(プロジェクト登録確認画面)'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'4. WA1020103(プロジェクト登録完了画面)'!$1:$4</definedName>
     <definedName name="引継項目格納先">データ!$B$2:$B$2</definedName>
     <definedName name="画面項目種類">データ!$A$2:$A$14</definedName>
     <definedName name="種別一覧">データ!$C$2:$C$7</definedName>
@@ -64,7 +63,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>作成者</author>
-    <author>山田　太郎</author>
   </authors>
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
@@ -100,21 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D50" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:z
-未登録カテゴリの指摘コメントの例。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E60" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
+    <comment ref="E60" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
       <text>
         <r>
           <rPr>
@@ -130,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
+    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
       <text>
         <r>
           <rPr>
@@ -148,7 +132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
+    <comment ref="A71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
       <text>
         <r>
           <rPr>
@@ -167,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="319">
   <si>
     <t>第１．２版</t>
   </si>
@@ -1242,7 +1226,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S23</t>
+    <t>システム機能設計書_サンプル_S22</t>
   </si>
   <si>
     <t>B5</t>
@@ -1260,23 +1244,6 @@
   </si>
   <si>
     <t>未</t>
-  </si>
-  <si>
-    <t>＜エラー＞</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>エラー内容</t>
-    <rPh sb="3" eb="5">
-      <t>ナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>未登録の指摘分類エイリアスが記入されています: z</t>
-  </si>
-  <si>
-    <t>2. WA1020101(プロジェクト登録画面)'!$D$50</t>
   </si>
   <si>
     <t>E60</t>
@@ -2025,7 +1992,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="300">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2785,10 +2752,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="11" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="5" quotePrefix="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -3225,190 +3188,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB5C215-5415-4123-8166-0557F0C27D3E}">
-  <sheetPr codeName="ErrorSheetTemplate">
-    <tabColor theme="3" tint="0.59999389629810485"/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="105.1640625" style="287" customWidth="1"/>
-    <col min="2" max="2" width="42.1640625" style="262" customWidth="1"/>
-    <col min="3" max="16384" width="9.33203125" style="262"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" s="286" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" s="287" t="s">
-        <v>313</v>
-      </c>
-      <c r="B2" s="262" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" s="287" t="s">
-        <v>314</v>
-      </c>
-      <c r="B3" s="299" t="s">
-        <v>315</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="10"/>
-  <hyperlinks>
-    <hyperlink ref="B3" location="'2. WA1020101(プロジェクト登録画面)'!$D$50" display="'2. WA1020101(プロジェクト登録画面)'!$D$50" xr:uid="{64D2E460-D4DB-4BC9-86C1-F753380C7804}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr codeName="Sheet6">
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A1" s="53" t="s">
-        <v>249</v>
-      </c>
-      <c r="B1" s="54" t="s">
-        <v>250</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>251</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="52" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="D3" s="52" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="B4" s="52" t="s">
-        <v>254</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="D4" s="52" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A5" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="B5" s="52" t="s">
-        <v>257</v>
-      </c>
-      <c r="C5" s="52" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A6" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A7" s="52" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="52" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A8" s="52" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A9" s="52" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A10" s="52" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A11" s="52" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A12" s="52" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A13" s="52" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A14" s="52" t="s">
-        <v>264</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="10"/>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC2E0AF-3204-4CF9-B73A-EABAF4691733}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{548803FF-18AB-4CC4-BD47-D79086AED9AB}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -3879,16 +3659,16 @@
         <v>38</v>
       </c>
       <c r="B16" s="297" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C16" s="272" t="s">
         <v>308</v>
       </c>
       <c r="D16" s="272" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E16" s="298" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F16" s="271"/>
       <c r="G16" s="271"/>
@@ -3946,16 +3726,16 @@
         <v>38</v>
       </c>
       <c r="B17" s="297" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C17" s="272" t="s">
         <v>308</v>
       </c>
       <c r="D17" s="272" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E17" s="298" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F17" s="271"/>
       <c r="G17" s="271"/>
@@ -3963,7 +3743,7 @@
       <c r="I17" s="271"/>
       <c r="J17" s="271"/>
       <c r="K17" s="272" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="L17" s="295">
         <f t="shared" si="1"/>
@@ -4079,14 +3859,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{311D7A0A-E9C9-4F32-8FFF-CF6AD8A51FE5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{82A4379E-7014-4858-A18B-47ECE65624E7}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{F3BFC1F9-C204-4384-8C62-86924A07F334}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{8BFCFE0C-1971-46DF-A117-6DEE36B5CA0F}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{AB8D5EE2-883F-4CA6-AFDB-2DE0E28DC746}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{791FA095-134F-4639-A9E4-66E14E83ACD0}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{C9DCF80E-EB03-4DF5-AED8-94ACEEF6669E}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{84143BC5-92D1-46BE-87D2-EDDEF4410448}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>
@@ -4094,7 +3874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
@@ -4774,7 +4554,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
@@ -6335,7 +6115,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4">
     <pageSetUpPr fitToPage="1"/>
@@ -7081,7 +6861,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet5">
     <pageSetUpPr fitToPage="1"/>
@@ -7587,7 +7367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet7">
     <pageSetUpPr fitToPage="1"/>
@@ -11888,7 +11668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet8">
     <pageSetUpPr fitToPage="1"/>
@@ -15407,7 +15187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
@@ -16577,4 +16357,143 @@
     <brk id="33" max="34" man="1"/>
   </rowBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr codeName="Sheet6">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A1" s="53" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="52" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A7" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A8" s="52" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10" s="52" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" s="52" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" s="52" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A13" s="52" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A14" s="52" t="s">
+        <v>264</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>
--- a/doctool/test/auto/scenario23/システム機能設計書_サンプル_S23_expected.xlsx
+++ b/doctool/test/auto/scenario23/システム機能設計書_サンプル_S23_expected.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario22\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario23\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74851ADB-FEE4-4550-B7BD-5ED0E19B2FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE652E60-A65E-4145-9FB2-C587B371AFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="レビュー結果1回目" sheetId="9" r:id="rId1"/>
@@ -1226,7 +1226,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S22</t>
+    <t>システム機能設計書_サンプル_S23</t>
   </si>
   <si>
     <t>B5</t>
@@ -3188,7 +3188,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{548803FF-18AB-4CC4-BD47-D79086AED9AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DA08FD-B997-4C3E-B410-2D2DC2F03579}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -3859,14 +3859,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{82A4379E-7014-4858-A18B-47ECE65624E7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{60383C70-D10D-4144-91C4-E1478FC254C0}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{791FA095-134F-4639-A9E4-66E14E83ACD0}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{C9DCF80E-EB03-4DF5-AED8-94ACEEF6669E}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{84143BC5-92D1-46BE-87D2-EDDEF4410448}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{8FFCBFE5-8F7B-45DF-A9FD-C258F72E783B}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{B1B1609A-1FDC-48BE-A0F3-F2E1AAD0D943}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{4D155F30-C673-4046-8D85-E888D9BC3EEE}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>
